--- a/bruno/testdata/servers.xlsx
+++ b/bruno/testdata/servers.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
-    <t>server_name</t>
-  </si>
-  <si>
-    <t>ipv4</t>
+    <t>Server Name</t>
+  </si>
+  <si>
+    <t>IPv4</t>
   </si>
   <si>
     <t>import-srv-01</t>
